--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260709.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260709.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>65.40%</t>
+          <t>64.81%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.40%</t>
+          <t>6.36%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.19%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -880,117 +880,117 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>12,839,134</t>
+          <t>1,995,288</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>1,180,617</t>
+          <t>12,839,134</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>1,995,288</t>
+          <t>1,180,617</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>5,281,520</t>
+          <t>1,334,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>1,334,000</t>
+          <t>5,281,520</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1019,105 +1019,105 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>601,600</t>
+          <t>854,349</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>854,349</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>164,000</t>
+          <t>601,600</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>140,482</t>
+          <t>164,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>140,482</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>312,672</t>
+          <t>1,902,321</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,44 +1151,44 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,902,321</t>
+          <t>137,921</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>137,921</t>
+          <t>312,672</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
@@ -1232,95 +1232,95 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>3,213,000</t>
+          <t>375,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>805,897</t>
+          <t>575,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>575,000</t>
+          <t>3,213,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>375,000</t>
+          <t>805,897</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1393,66 +1393,66 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>767,000</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>767,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>580,000</t>
+          <t>10,569,121</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
@@ -1474,51 +1474,51 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>10,569,121</t>
+          <t>4,440,578</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>4,440,578</t>
+          <t>580,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,374,384</t>
+          <t>145,386</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>145,386</t>
+          <t>1,374,384</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>202607WVHFN6F</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>774,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>202607WVHFN6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>774,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,44 +1723,44 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>389,000</t>
+          <t>181,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>181,000</t>
+          <t>1,182,076</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
@@ -1811,39 +1811,39 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>1,182,076</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>1,555,400</t>
+          <t>93,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>289,000</t>
+          <t>389,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>289,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,39 +1899,39 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>93,000</t>
+          <t>1,555,400</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>319,000</t>
+          <t>1,000,121</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,000,121</t>
+          <t>319,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,752,000</t>
+          <t>177,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>177,000</t>
+          <t>1,752,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>253,000</t>
+          <t>156,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>156,000</t>
+          <t>330,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>330,000</t>
+          <t>253,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>315,758,488</t>
+          <t>572,516,139</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr"/>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>407,047,375</t>
+          <t>408,244,975</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>-138,344,607</t>
+          <t>-138,303,708</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
